--- a/Daily_Report/Top 7 broker List with its Turnover 2024-10-16.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-10-16.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="284">
   <si>
     <t>Date: 2024-10-16</t>
   </si>
@@ -65,19 +65,19 @@
     <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
+    <t>Sundhara Securities Limited</t>
+  </si>
+  <si>
     <t>Sani Securities Company Limited</t>
   </si>
   <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Online Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
-  </si>
-  <si>
-    <t>Linch Stock Market Limited</t>
+    <t>Nepal Stock House Pvt. Limited</t>
+  </si>
+  <si>
+    <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Dynamic Money Managers Securities Pvt.Ltd</t>
   </si>
   <si>
     <t>58</t>
@@ -86,82 +86,82 @@
     <t>34</t>
   </si>
   <si>
+    <t>52</t>
+  </si>
+  <si>
     <t>42</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>567,535,909.13</t>
-  </si>
-  <si>
-    <t>471,896,021.47</t>
-  </si>
-  <si>
-    <t>424,538,231.06</t>
-  </si>
-  <si>
-    <t>349,090,538.1</t>
-  </si>
-  <si>
-    <t>327,869,748.39</t>
-  </si>
-  <si>
-    <t>326,653,757.7</t>
-  </si>
-  <si>
-    <t>323,478,649.5</t>
-  </si>
-  <si>
-    <t>316,947,881.5</t>
-  </si>
-  <si>
-    <t>279,998,527.85</t>
-  </si>
-  <si>
-    <t>232,309,729.3</t>
-  </si>
-  <si>
-    <t>156,732,454.6</t>
-  </si>
-  <si>
-    <t>174,452,832.7</t>
-  </si>
-  <si>
-    <t>175,698,830.5</t>
-  </si>
-  <si>
-    <t>138,894,525.3</t>
-  </si>
-  <si>
-    <t>250,588,027.63</t>
-  </si>
-  <si>
-    <t>191,897,493.62</t>
-  </si>
-  <si>
-    <t>192,228,501.76</t>
-  </si>
-  <si>
-    <t>192,358,083.5</t>
-  </si>
-  <si>
-    <t>153,416,915.69</t>
-  </si>
-  <si>
-    <t>150,954,927.19</t>
-  </si>
-  <si>
-    <t>184,584,124.2</t>
+    <t>14</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>594,362,957.4</t>
+  </si>
+  <si>
+    <t>447,766,708.9</t>
+  </si>
+  <si>
+    <t>399,592,411.1</t>
+  </si>
+  <si>
+    <t>355,757,775.31</t>
+  </si>
+  <si>
+    <t>279,581,417.81</t>
+  </si>
+  <si>
+    <t>278,205,283.89</t>
+  </si>
+  <si>
+    <t>274,705,223.1</t>
+  </si>
+  <si>
+    <t>145,603,609.0</t>
+  </si>
+  <si>
+    <t>334,371,598.1</t>
+  </si>
+  <si>
+    <t>336,290,990.3</t>
+  </si>
+  <si>
+    <t>183,769,869.8</t>
+  </si>
+  <si>
+    <t>205,289,834.01</t>
+  </si>
+  <si>
+    <t>96,127,745.85</t>
+  </si>
+  <si>
+    <t>164,367,283.4</t>
+  </si>
+  <si>
+    <t>448,759,348.4</t>
+  </si>
+  <si>
+    <t>113,395,110.8</t>
+  </si>
+  <si>
+    <t>63,301,420.8</t>
+  </si>
+  <si>
+    <t>171,987,905.51</t>
+  </si>
+  <si>
+    <t>74,291,583.8</t>
+  </si>
+  <si>
+    <t>182,077,538.05</t>
+  </si>
+  <si>
+    <t>110,337,939.7</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,331 +179,355 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>23,766,562.9</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>16,952,003.6</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>15,366,416.9</t>
-  </si>
-  <si>
-    <t>NGPL</t>
-  </si>
-  <si>
-    <t>14,635,259.0</t>
+    <t>TSHL</t>
+  </si>
+  <si>
+    <t>18,925,980.0</t>
+  </si>
+  <si>
+    <t>NLIC</t>
+  </si>
+  <si>
+    <t>12,926,216.1</t>
+  </si>
+  <si>
+    <t>LEC</t>
+  </si>
+  <si>
+    <t>11,151,900.0</t>
   </si>
   <si>
     <t>SBI</t>
   </si>
   <si>
-    <t>13,231,745.0</t>
+    <t>9,223,600.0</t>
+  </si>
+  <si>
+    <t>FMDBL</t>
+  </si>
+  <si>
+    <t>8,192,478.0</t>
+  </si>
+  <si>
+    <t>CIT</t>
+  </si>
+  <si>
+    <t>149,695,059.6</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>53,118,249.7</t>
+  </si>
+  <si>
+    <t>NICA</t>
+  </si>
+  <si>
+    <t>24,318,584.8</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>17,646,643.1</t>
+  </si>
+  <si>
+    <t>MKCL</t>
+  </si>
+  <si>
+    <t>6,097,171.6</t>
+  </si>
+  <si>
+    <t>CZBIL</t>
+  </si>
+  <si>
+    <t>123,065,554.2</t>
+  </si>
+  <si>
+    <t>MBL</t>
+  </si>
+  <si>
+    <t>100,913,069.9</t>
+  </si>
+  <si>
+    <t>NABIL</t>
+  </si>
+  <si>
+    <t>67,282,729.3</t>
+  </si>
+  <si>
+    <t>SBL</t>
+  </si>
+  <si>
+    <t>8,737,950.19</t>
+  </si>
+  <si>
+    <t>ADBL</t>
+  </si>
+  <si>
+    <t>6,786,407.9</t>
+  </si>
+  <si>
+    <t>38,055,546.7</t>
+  </si>
+  <si>
+    <t>SPDL</t>
+  </si>
+  <si>
+    <t>28,704,605.2</t>
+  </si>
+  <si>
+    <t>PRVU</t>
+  </si>
+  <si>
+    <t>18,820,009.5</t>
+  </si>
+  <si>
+    <t>10,169,616.8</t>
+  </si>
+  <si>
+    <t>RURU</t>
+  </si>
+  <si>
+    <t>8,094,515.4</t>
+  </si>
+  <si>
+    <t>NMB</t>
+  </si>
+  <si>
+    <t>136,719,867.5</t>
+  </si>
+  <si>
+    <t>HDHPC</t>
+  </si>
+  <si>
+    <t>30,404,570.4</t>
+  </si>
+  <si>
+    <t>USHL</t>
+  </si>
+  <si>
+    <t>8,130,060.0</t>
+  </si>
+  <si>
+    <t>NYADI</t>
+  </si>
+  <si>
+    <t>4,143,185.0</t>
+  </si>
+  <si>
+    <t>SARBTM</t>
+  </si>
+  <si>
+    <t>2,430,000.0</t>
+  </si>
+  <si>
+    <t>MKHL</t>
+  </si>
+  <si>
+    <t>59,905,876.5</t>
+  </si>
+  <si>
+    <t>NTC</t>
+  </si>
+  <si>
+    <t>4,847,053.0</t>
+  </si>
+  <si>
+    <t>2,559,150.0</t>
+  </si>
+  <si>
+    <t>ALICL</t>
+  </si>
+  <si>
+    <t>1,730,052.0</t>
   </si>
   <si>
     <t>SAHAS</t>
   </si>
   <si>
-    <t>9,697,137.1</t>
+    <t>1,204,447.0</t>
+  </si>
+  <si>
+    <t>116,672,048.0</t>
+  </si>
+  <si>
+    <t>JBBL</t>
+  </si>
+  <si>
+    <t>17,390,000.0</t>
+  </si>
+  <si>
+    <t>3,888,947.0</t>
+  </si>
+  <si>
+    <t>TPC</t>
+  </si>
+  <si>
+    <t>3,215,670.0</t>
+  </si>
+  <si>
+    <t>HEI</t>
+  </si>
+  <si>
+    <t>2,359,000.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>184,647,351.0</t>
+  </si>
+  <si>
+    <t>36,386,090.0</t>
+  </si>
+  <si>
+    <t>24,587,079.9</t>
+  </si>
+  <si>
+    <t>ILI</t>
+  </si>
+  <si>
+    <t>20,318,160.2</t>
+  </si>
+  <si>
+    <t>14,863,434.9</t>
+  </si>
+  <si>
+    <t>27,776,766.4</t>
+  </si>
+  <si>
+    <t>13,573,470.0</t>
+  </si>
+  <si>
+    <t>7,539,804.0</t>
+  </si>
+  <si>
+    <t>RLFL</t>
+  </si>
+  <si>
+    <t>5,872,548.0</t>
+  </si>
+  <si>
+    <t>3,491,232.5</t>
+  </si>
+  <si>
+    <t>SFCL</t>
+  </si>
+  <si>
+    <t>25,530,400.0</t>
+  </si>
+  <si>
+    <t>NICLBSL</t>
+  </si>
+  <si>
+    <t>7,097,000.0</t>
+  </si>
+  <si>
+    <t>4,874,161.0</t>
+  </si>
+  <si>
+    <t>RADHI</t>
+  </si>
+  <si>
+    <t>3,952,370.6</t>
   </si>
   <si>
     <t>KBL</t>
   </si>
   <si>
-    <t>9,345,291.9</t>
-  </si>
-  <si>
-    <t>MNBBL</t>
-  </si>
-  <si>
-    <t>8,751,154.5</t>
-  </si>
-  <si>
-    <t>HIDCLP</t>
-  </si>
-  <si>
-    <t>8,041,858.9</t>
-  </si>
-  <si>
-    <t>SHINE</t>
-  </si>
-  <si>
-    <t>7,467,540.1</t>
-  </si>
-  <si>
-    <t>FMDBL</t>
-  </si>
-  <si>
-    <t>17,115,454.6</t>
-  </si>
-  <si>
-    <t>MKCL</t>
-  </si>
-  <si>
-    <t>16,540,911.3</t>
-  </si>
-  <si>
-    <t>AKPL</t>
-  </si>
-  <si>
-    <t>13,919,717.0</t>
-  </si>
-  <si>
-    <t>8,399,008.5</t>
-  </si>
-  <si>
-    <t>HDHPC</t>
-  </si>
-  <si>
-    <t>8,078,643.2</t>
-  </si>
-  <si>
-    <t>6,854,216.5</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>5,598,084.0</t>
-  </si>
-  <si>
-    <t>5,448,147.4</t>
-  </si>
-  <si>
-    <t>UPPER</t>
-  </si>
-  <si>
-    <t>5,431,709.1</t>
-  </si>
-  <si>
-    <t>GFCL</t>
-  </si>
-  <si>
-    <t>4,511,649.0</t>
-  </si>
-  <si>
-    <t>NIMB</t>
-  </si>
-  <si>
-    <t>7,429,873.9</t>
-  </si>
-  <si>
-    <t>PROFL</t>
-  </si>
-  <si>
-    <t>6,853,847.8</t>
-  </si>
-  <si>
-    <t>6,020,081.5</t>
-  </si>
-  <si>
-    <t>5,003,609.9</t>
-  </si>
-  <si>
-    <t>LEC</t>
-  </si>
-  <si>
-    <t>4,726,046.2</t>
-  </si>
-  <si>
-    <t>12,093,369.0</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>6,135,010.0</t>
-  </si>
-  <si>
-    <t>HIDCL</t>
-  </si>
-  <si>
-    <t>5,960,068.0</t>
-  </si>
-  <si>
-    <t>5,939,806.0</t>
-  </si>
-  <si>
-    <t>5,482,379.6</t>
-  </si>
-  <si>
-    <t>24,695,993.1</t>
-  </si>
-  <si>
-    <t>12,112,738.2</t>
-  </si>
-  <si>
-    <t>NLG</t>
-  </si>
-  <si>
-    <t>6,759,684.3</t>
-  </si>
-  <si>
-    <t>4,446,148.5</t>
-  </si>
-  <si>
-    <t>3,633,296.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>SARBTM</t>
-  </si>
-  <si>
-    <t>22,766,647.7</t>
-  </si>
-  <si>
-    <t>RHPL</t>
-  </si>
-  <si>
-    <t>14,702,087.1</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>6,367,797.8</t>
-  </si>
-  <si>
-    <t>6,025,955.5</t>
-  </si>
-  <si>
-    <t>5,348,860.3</t>
-  </si>
-  <si>
-    <t>12,947,775.1</t>
-  </si>
-  <si>
-    <t>7,564,351.1</t>
-  </si>
-  <si>
-    <t>7,117,869.3</t>
-  </si>
-  <si>
-    <t>NTC</t>
-  </si>
-  <si>
-    <t>6,923,072.6</t>
-  </si>
-  <si>
-    <t>HEI</t>
-  </si>
-  <si>
-    <t>6,255,762.6</t>
-  </si>
-  <si>
-    <t>CGH</t>
-  </si>
-  <si>
-    <t>12,442,087.0</t>
-  </si>
-  <si>
-    <t>11,125,764.2</t>
-  </si>
-  <si>
-    <t>7,190,778.1</t>
-  </si>
-  <si>
-    <t>GBIME</t>
-  </si>
-  <si>
-    <t>6,841,157.4</t>
-  </si>
-  <si>
-    <t>EHPL</t>
-  </si>
-  <si>
-    <t>6,485,179.0</t>
-  </si>
-  <si>
-    <t>16,073,014.0</t>
-  </si>
-  <si>
-    <t>9,609,352.5</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>8,103,157.4</t>
-  </si>
-  <si>
-    <t>6,004,683.1</t>
-  </si>
-  <si>
-    <t>5,544,329.7</t>
+    <t>3,617,950.0</t>
+  </si>
+  <si>
+    <t>39,979,172.0</t>
+  </si>
+  <si>
+    <t>SALICO</t>
+  </si>
+  <si>
+    <t>21,961,384.0</t>
+  </si>
+  <si>
+    <t>19,880,392.39</t>
+  </si>
+  <si>
+    <t>13,983,860.0</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>4,327,020.8</t>
+  </si>
+  <si>
+    <t>VLBS</t>
+  </si>
+  <si>
+    <t>12,649,094.3</t>
+  </si>
+  <si>
+    <t>11,375,268.0</t>
+  </si>
+  <si>
+    <t>DOLTI</t>
+  </si>
+  <si>
+    <t>6,030,095.0</t>
+  </si>
+  <si>
+    <t>5,764,156.8</t>
+  </si>
+  <si>
+    <t>5,664,816.0</t>
+  </si>
+  <si>
+    <t>45,539,083.0</t>
+  </si>
+  <si>
+    <t>29,860,367.5</t>
+  </si>
+  <si>
+    <t>MPFL</t>
+  </si>
+  <si>
+    <t>18,371,969.0</t>
+  </si>
+  <si>
+    <t>BEDC</t>
+  </si>
+  <si>
+    <t>13,399,702.0</t>
+  </si>
+  <si>
+    <t>7,268,902.8</t>
   </si>
   <si>
     <t>PCBL</t>
   </si>
   <si>
-    <t>7,263,394.6</t>
-  </si>
-  <si>
-    <t>6,726,215.8</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>6,318,234.2</t>
-  </si>
-  <si>
-    <t>5,613,823.4</t>
-  </si>
-  <si>
-    <t>NABIL</t>
-  </si>
-  <si>
-    <t>5,387,603.0</t>
-  </si>
-  <si>
-    <t>7,833,931.7</t>
-  </si>
-  <si>
-    <t>MPFL</t>
-  </si>
-  <si>
-    <t>6,341,413.4</t>
-  </si>
-  <si>
-    <t>NHPC</t>
-  </si>
-  <si>
-    <t>4,205,844.2</t>
-  </si>
-  <si>
-    <t>4,187,264.5</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>3,587,934.7</t>
-  </si>
-  <si>
-    <t>68,494,047.5</t>
-  </si>
-  <si>
-    <t>35,186,092.1</t>
-  </si>
-  <si>
-    <t>2,459,341.0</t>
-  </si>
-  <si>
-    <t>2,397,590.5</t>
-  </si>
-  <si>
-    <t>2,278,519.1</t>
+    <t>28,359,274.0</t>
+  </si>
+  <si>
+    <t>RIDI</t>
+  </si>
+  <si>
+    <t>11,690,440.0</t>
+  </si>
+  <si>
+    <t>10,422,270.0</t>
+  </si>
+  <si>
+    <t>NIFRA</t>
+  </si>
+  <si>
+    <t>6,909,703.6</t>
+  </si>
+  <si>
+    <t>6,137,064.2</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -521,112 +545,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>150,950,397.9</t>
-  </si>
-  <si>
-    <t>150,404,104.69</t>
-  </si>
-  <si>
-    <t>NICA</t>
-  </si>
-  <si>
-    <t>147,506,063.3</t>
-  </si>
-  <si>
-    <t>132,064,892.9</t>
-  </si>
-  <si>
-    <t>131,318,383.7</t>
+    <t>2,409,733,596.0</t>
+  </si>
+  <si>
+    <t>327,894,753.1</t>
+  </si>
+  <si>
+    <t>263,240,616.9</t>
+  </si>
+  <si>
+    <t>219,799,645.5</t>
+  </si>
+  <si>
+    <t>196,858,603.3</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>2,435,213,079.19</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>1,498,119,550.36</t>
+    <t>1,225,616,595.15</t>
+  </si>
+  <si>
+    <t>Commercial Banks</t>
+  </si>
+  <si>
+    <t>1,088,918,898.3</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,342,472,047.16</t>
+    <t>944,197,331.85</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>600,434,738.9</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>748,026,630.0</t>
-  </si>
-  <si>
-    <t>Commercial Banks</t>
-  </si>
-  <si>
-    <t>679,999,095.67</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>260,683,259.8</t>
+    <t>335,964,571.0</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>206,447,027.0</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>252,922,893.8</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>225,267,038.4</t>
+    <t>132,056,154.0</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>60,491,964.7</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>60,042,775.8</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>147,388,379.8</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>145,347,504.8</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>141,389,973.6</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>130,100,056.8</t>
+    <t>54,204,290.6</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>59,071,157.4</t>
+    <t>29,195,351.0</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>19,881,839.5</t>
+    <t>11,291,953.0</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>7,151,344.5</t>
+    <t>8,336,544.63</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>2,416,966.0</t>
+    <t>1,225,738.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -638,214 +659,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>91,322,673.2</t>
-  </si>
-  <si>
-    <t>65,167,053.3</t>
-  </si>
-  <si>
-    <t>54,542,188.3</t>
-  </si>
-  <si>
-    <t>33,257,394.1</t>
-  </si>
-  <si>
-    <t>18,741,164.1</t>
-  </si>
-  <si>
-    <t>73,287,809.0</t>
-  </si>
-  <si>
-    <t>70,792,807.5</t>
-  </si>
-  <si>
-    <t>32,122,017.9</t>
-  </si>
-  <si>
-    <t>32,027,503.3</t>
-  </si>
-  <si>
-    <t>22,463,403.1</t>
-  </si>
-  <si>
-    <t>67,211,765.2</t>
-  </si>
-  <si>
-    <t>62,720,178.8</t>
-  </si>
-  <si>
-    <t>26,142,922.1</t>
-  </si>
-  <si>
-    <t>25,629,241.3</t>
-  </si>
-  <si>
-    <t>10,055,419.6</t>
-  </si>
-  <si>
-    <t>55,477,576.0</t>
-  </si>
-  <si>
-    <t>32,787,054.7</t>
-  </si>
-  <si>
-    <t>25,494,218.4</t>
-  </si>
-  <si>
-    <t>11,486,929.5</t>
-  </si>
-  <si>
-    <t>6,274,084.7</t>
-  </si>
-  <si>
-    <t>48,786,839.5</t>
-  </si>
-  <si>
-    <t>48,341,290.1</t>
-  </si>
-  <si>
-    <t>22,803,841.1</t>
-  </si>
-  <si>
-    <t>13,613,922.0</t>
-  </si>
-  <si>
-    <t>9,506,038.4</t>
-  </si>
-  <si>
-    <t>58,181,997.4</t>
-  </si>
-  <si>
-    <t>35,288,202.29</t>
-  </si>
-  <si>
-    <t>31,986,452.8</t>
-  </si>
-  <si>
-    <t>16,591,741.4</t>
-  </si>
-  <si>
-    <t>8,890,998.5</t>
-  </si>
-  <si>
-    <t>52,032,706.8</t>
-  </si>
-  <si>
-    <t>34,224,411.5</t>
-  </si>
-  <si>
-    <t>19,043,653.5</t>
-  </si>
-  <si>
-    <t>8,627,854.6</t>
-  </si>
-  <si>
-    <t>7,797,204.3</t>
-  </si>
-  <si>
-    <t>75,116,977.0</t>
-  </si>
-  <si>
-    <t>72,865,907.9</t>
-  </si>
-  <si>
-    <t>28,380,319.8</t>
-  </si>
-  <si>
-    <t>24,239,321.73</t>
-  </si>
-  <si>
-    <t>13,466,553.7</t>
-  </si>
-  <si>
-    <t>67,795,185.3</t>
-  </si>
-  <si>
-    <t>42,820,151.7</t>
-  </si>
-  <si>
-    <t>21,029,149.8</t>
-  </si>
-  <si>
-    <t>14,720,380.9</t>
-  </si>
-  <si>
-    <t>9,059,275.5</t>
-  </si>
-  <si>
-    <t>56,664,462.05</t>
-  </si>
-  <si>
-    <t>55,958,624.1</t>
-  </si>
-  <si>
-    <t>17,845,664.89</t>
-  </si>
-  <si>
-    <t>13,682,906.5</t>
-  </si>
-  <si>
-    <t>12,649,873.0</t>
-  </si>
-  <si>
-    <t>48,658,355.1</t>
-  </si>
-  <si>
-    <t>46,028,068.6</t>
-  </si>
-  <si>
-    <t>26,620,701.5</t>
-  </si>
-  <si>
-    <t>26,544,597.6</t>
-  </si>
-  <si>
-    <t>18,476,025.0</t>
-  </si>
-  <si>
-    <t>43,226,584.9</t>
-  </si>
-  <si>
-    <t>35,698,916.9</t>
-  </si>
-  <si>
-    <t>25,343,537.1</t>
-  </si>
-  <si>
-    <t>15,823,323.5</t>
-  </si>
-  <si>
-    <t>7,175,459.5</t>
-  </si>
-  <si>
-    <t>48,177,265.9</t>
-  </si>
-  <si>
-    <t>29,304,917.8</t>
-  </si>
-  <si>
-    <t>26,191,397.4</t>
-  </si>
-  <si>
-    <t>17,628,914.39</t>
-  </si>
-  <si>
-    <t>6,525,269.2</t>
-  </si>
-  <si>
-    <t>113,141,126.7</t>
-  </si>
-  <si>
-    <t>23,302,732.8</t>
-  </si>
-  <si>
-    <t>17,393,455.0</t>
-  </si>
-  <si>
-    <t>9,384,178.6</t>
-  </si>
-  <si>
-    <t>5,734,891.7</t>
+    <t>45,325,502.5</t>
+  </si>
+  <si>
+    <t>32,457,138.3</t>
+  </si>
+  <si>
+    <t>14,564,733.3</t>
+  </si>
+  <si>
+    <t>13,697,150.6</t>
+  </si>
+  <si>
+    <t>11,758,416.5</t>
+  </si>
+  <si>
+    <t>154,593,192.3</t>
+  </si>
+  <si>
+    <t>92,025,982.9</t>
+  </si>
+  <si>
+    <t>34,773,973.6</t>
+  </si>
+  <si>
+    <t>30,441,424.9</t>
+  </si>
+  <si>
+    <t>10,015,639.19</t>
+  </si>
+  <si>
+    <t>313,217,548.6</t>
+  </si>
+  <si>
+    <t>9,631,144.0</t>
+  </si>
+  <si>
+    <t>6,010,630.8</t>
+  </si>
+  <si>
+    <t>4,015,929.5</t>
+  </si>
+  <si>
+    <t>1,182,283.89</t>
+  </si>
+  <si>
+    <t>65,570,013.9</t>
+  </si>
+  <si>
+    <t>63,794,770.2</t>
+  </si>
+  <si>
+    <t>25,414,980.2</t>
+  </si>
+  <si>
+    <t>5,724,751.2</t>
+  </si>
+  <si>
+    <t>5,168,205.59</t>
+  </si>
+  <si>
+    <t>139,250,930.9</t>
+  </si>
+  <si>
+    <t>38,691,266.2</t>
+  </si>
+  <si>
+    <t>17,937,375.2</t>
+  </si>
+  <si>
+    <t>2,547,039.2</t>
+  </si>
+  <si>
+    <t>2,207,917.5</t>
+  </si>
+  <si>
+    <t>70,947,620.34</t>
+  </si>
+  <si>
+    <t>6,412,994.0</t>
+  </si>
+  <si>
+    <t>5,923,095.7</t>
+  </si>
+  <si>
+    <t>4,156,133.0</t>
+  </si>
+  <si>
+    <t>1,940,835.0</t>
+  </si>
+  <si>
+    <t>122,059,547.4</t>
+  </si>
+  <si>
+    <t>18,337,902.0</t>
+  </si>
+  <si>
+    <t>8,321,328.5</t>
+  </si>
+  <si>
+    <t>5,224,249.9</t>
+  </si>
+  <si>
+    <t>2,676,790.0</t>
+  </si>
+  <si>
+    <t>201,569,826.1</t>
+  </si>
+  <si>
+    <t>115,071,435.5</t>
+  </si>
+  <si>
+    <t>56,208,551.2</t>
+  </si>
+  <si>
+    <t>29,894,804.7</t>
+  </si>
+  <si>
+    <t>20,340,434.2</t>
+  </si>
+  <si>
+    <t>45,258,117.7</t>
+  </si>
+  <si>
+    <t>30,990,539.6</t>
+  </si>
+  <si>
+    <t>10,631,931.9</t>
+  </si>
+  <si>
+    <t>10,391,094.0</t>
+  </si>
+  <si>
+    <t>5,928,481.5</t>
+  </si>
+  <si>
+    <t>26,889,712.0</t>
+  </si>
+  <si>
+    <t>11,455,436.0</t>
+  </si>
+  <si>
+    <t>7,805,144.0</t>
+  </si>
+  <si>
+    <t>7,555,091.0</t>
+  </si>
+  <si>
+    <t>7,530,879.1</t>
+  </si>
+  <si>
+    <t>62,093,887.5</t>
+  </si>
+  <si>
+    <t>56,551,094.3</t>
+  </si>
+  <si>
+    <t>17,112,257.3</t>
+  </si>
+  <si>
+    <t>14,806,799.4</t>
+  </si>
+  <si>
+    <t>6,062,500.6</t>
+  </si>
+  <si>
+    <t>25,378,399.1</t>
+  </si>
+  <si>
+    <t>14,711,848.8</t>
+  </si>
+  <si>
+    <t>13,506,393.3</t>
+  </si>
+  <si>
+    <t>8,067,430.1</t>
+  </si>
+  <si>
+    <t>5,314,275.0</t>
+  </si>
+  <si>
+    <t>72,842,904.95</t>
+  </si>
+  <si>
+    <t>39,810,026.29</t>
+  </si>
+  <si>
+    <t>20,880,594.2</t>
+  </si>
+  <si>
+    <t>20,844,128.89</t>
+  </si>
+  <si>
+    <t>8,441,841.9</t>
+  </si>
+  <si>
+    <t>41,667,638.5</t>
+  </si>
+  <si>
+    <t>23,994,158.4</t>
+  </si>
+  <si>
+    <t>23,217,435.7</t>
+  </si>
+  <si>
+    <t>7,155,799.6</t>
+  </si>
+  <si>
+    <t>3,574,958.6</t>
   </si>
 </sst>
 </file>
@@ -1654,7 +1675,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.04187675619756426</v>
+        <v>0.03184246219311917</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1663,7 +1684,7 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.02054930887061204</v>
+        <v>0.3343148488366773</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>74</v>
@@ -1672,43 +1693,43 @@
         <v>75</v>
       </c>
       <c r="J9" s="14">
-        <v>0.04031546124189007</v>
+        <v>0.3079777062362734</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M9" s="16">
-        <v>0.01963449521521133</v>
+        <v>0.1069703864289099</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P9" s="18">
-        <v>0.02266105347095207</v>
+        <v>0.4890162893190316</v>
       </c>
       <c r="Q9" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="S9" s="16">
+        <v>0.2153297581563296</v>
+      </c>
+      <c r="T9" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="R9" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="S9" s="16">
-        <v>0.03702198035360302</v>
-      </c>
-      <c r="T9" s="17" t="s">
-        <v>89</v>
-      </c>
       <c r="U9" s="17" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="V9" s="18">
-        <v>0.07634504823787451</v>
+        <v>0.4247172539472548</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1720,7 +1741,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.02986948196103829</v>
+        <v>0.02174801767012003</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1729,7 +1750,7 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.01980370987423998</v>
+        <v>0.1186292965604616</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>76</v>
@@ -1738,43 +1759,43 @@
         <v>77</v>
       </c>
       <c r="J10" s="14">
-        <v>0.03896212423248702</v>
+        <v>0.2525400060081371</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M10" s="16">
-        <v>0.01603619516721585</v>
+        <v>0.08068581262907717</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P10" s="18">
-        <v>0.02090417866682329</v>
+        <v>0.1087503262490162</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="S10" s="16">
-        <v>0.01878138504573523</v>
+        <v>0.01742257706989583</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="V10" s="18">
-        <v>0.03744524783543712</v>
+        <v>0.06330422044312414</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1786,7 +1807,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.02707567336762151</v>
+        <v>0.01876277762797201</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>68</v>
@@ -1795,7 +1816,7 @@
         <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.01854466683728195</v>
+        <v>0.05431083713155433</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>78</v>
@@ -1804,43 +1825,43 @@
         <v>79</v>
       </c>
       <c r="J11" s="14">
-        <v>0.03278789984413141</v>
+        <v>0.1683783961631898</v>
       </c>
       <c r="K11" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="16">
+        <v>0.05290118953436965</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="O11" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="P11" s="18">
+        <v>0.02907940042540698</v>
+      </c>
+      <c r="Q11" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="L11" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="M11" s="16">
-        <v>0.01560668882534803</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="O11" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="P11" s="18">
-        <v>0.01836119840082203</v>
-      </c>
-      <c r="Q11" s="15" t="s">
-        <v>102</v>
-      </c>
       <c r="R11" s="15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01824582714726872</v>
+        <v>0.009198782870421248</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="V11" s="18">
-        <v>0.02089684840235491</v>
+        <v>0.01415680035535516</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1852,7 +1873,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02578737092148938</v>
+        <v>0.01551846373527046</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>70</v>
@@ -1861,52 +1882,52 @@
         <v>71</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01704159080415398</v>
+        <v>0.03941035085737255</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01978386841399207</v>
+        <v>0.02186715752670609</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01555959989509667</v>
+        <v>0.02858578928074982</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01526096849257228</v>
+        <v>0.01481924311155635</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01818379816544202</v>
+        <v>0.006218616611975859</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01374479739813554</v>
+        <v>0.01170589318874877</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1918,7 +1939,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02331437497987309</v>
+        <v>0.01378362816525013</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>72</v>
@@ -1927,52 +1948,52 @@
         <v>73</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01582454557836262</v>
+        <v>0.01361684886082427</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01902924780137939</v>
+        <v>0.01698332528718036</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01292400826603785</v>
+        <v>0.02275288401763421</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01441440152091812</v>
+        <v>0.008691564765049576</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="S13" s="16">
-        <v>0.0167834579298948</v>
+        <v>0.004329346240716746</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01123194994666874</v>
+        <v>0.008587386775464627</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1983,7 +2004,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1992,7 +2013,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2001,7 +2022,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2010,7 +2031,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2019,7 +2040,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2028,7 +2049,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2037,7 +2058,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2046,566 +2067,566 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D16" s="10">
-        <v>0.04011490257048222</v>
+        <v>0.3106642981381733</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G16" s="12">
-        <v>0.02743777126932852</v>
+        <v>0.06203401424870869</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J16" s="14">
-        <v>0.02930734169437277</v>
+        <v>0.06389110326124509</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="M16" s="16">
-        <v>0.04604253695182006</v>
+        <v>0.1123775073226804</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="P16" s="18">
-        <v>0.0221532929934685</v>
+        <v>0.04524297215130429</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="S16" s="16">
-        <v>0.02398237128866802</v>
+        <v>0.1636887781627069</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="V16" s="18">
-        <v>0.2117420967531274</v>
+        <v>0.1032352922888418</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D17" s="10">
-        <v>0.02590512223717695</v>
+        <v>0.06121863677233261</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G17" s="12">
-        <v>0.01602969882313553</v>
+        <v>0.03031370963988162</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="J17" s="14">
-        <v>0.0262067427289666</v>
+        <v>0.01776059755605304</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="M17" s="16">
-        <v>0.02752682026932313</v>
+        <v>0.06173128326109894</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="P17" s="18">
-        <v>0.02051490213056814</v>
+        <v>0.04068678129292014</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="S17" s="16">
-        <v>0.0194132571584374</v>
+        <v>0.1073321364763626</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1087740787665184</v>
+        <v>0.0425563076962114</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D18" s="10">
-        <v>0.0112200791131639</v>
+        <v>0.04136711346809784</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G18" s="12">
-        <v>0.01508355437671878</v>
+        <v>0.01683868820556704</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J18" s="14">
-        <v>0.01693788114687774</v>
+        <v>0.01219783175206552</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="M18" s="16">
-        <v>0.02321219430381347</v>
+        <v>0.05588182122703188</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="P18" s="18">
-        <v>0.01927056165087782</v>
+        <v>0.0215682968032517</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="S18" s="16">
-        <v>0.01287554207125535</v>
+        <v>0.06603745530082653</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="V18" s="18">
-        <v>0.007602792344414063</v>
+        <v>0.03793983194926737</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D19" s="10">
-        <v>0.01061775193967452</v>
+        <v>0.0341847686620317</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G19" s="12">
-        <v>0.0146707585676056</v>
+        <v>0.01311519566612425</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01611434942600762</v>
+        <v>0.009891005159782425</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01720093341023155</v>
+        <v>0.03930725052408131</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01712211458176725</v>
+        <v>0.02061709553214029</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01281866319090564</v>
+        <v>0.0481648005104622</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="V19" s="18">
-        <v>0.007411897210854406</v>
+        <v>0.02515315698050883</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D20" s="10">
-        <v>0.009424708135560084</v>
+        <v>0.0250073372085957</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01325665467683478</v>
+        <v>0.007796989884702882</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01527584213984123</v>
+        <v>0.009054100877542916</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01588221133169693</v>
+        <v>0.01216282847572206</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01643214424719399</v>
+        <v>0.02026177578028357</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01098390762519613</v>
+        <v>0.02612783876029035</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="V20" s="18">
-        <v>0.007043800583197378</v>
+        <v>0.02234054427776914</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>170</v>
+        <v>64</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2646743157815167</v>
+        <v>0.4302315895714577</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2371759119307279</v>
+        <v>0.2165309395060276</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1321546310733533</v>
+        <v>0.1923804173571184</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1201361368910145</v>
+        <v>0.1668123099455447</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D35" s="22">
-        <v>0.04605517857815852</v>
+        <v>0.1060794204652242</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D36" s="22">
-        <v>0.04468414676646461</v>
+        <v>0.05935520495336163</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D37" s="22">
-        <v>0.03979815845959777</v>
+        <v>0.03647320776450914</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D38" s="22">
-        <v>0.0260392560582613</v>
+        <v>0.02333049601835155</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D39" s="22">
-        <v>0.02567869258114039</v>
+        <v>0.01068717737740274</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D40" s="22">
-        <v>0.02497951148955641</v>
+        <v>0.01060781871424693</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="D41" s="22">
-        <v>0.02298491032201128</v>
+        <v>0.009576327552450683</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D42" s="22">
-        <v>0.01043616189609852</v>
+        <v>0.005157972571727903</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D43" s="22">
-        <v>0.003512544953355635</v>
+        <v>0.001994960905085217</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D44" s="22">
-        <v>0.001263435359348041</v>
+        <v>0.001472825880549459</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D45" s="22">
-        <v>0.0004270078593951106</v>
+        <v>0.000216552388225256</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -2984,331 +3005,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1609108282504845</v>
+        <v>0.0762589625340605</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1553049944598</v>
+        <v>0.3452538771356612</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1583173440756646</v>
+        <v>0.7838425853428326</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="M9" s="16">
-        <v>0.158920308473408</v>
+        <v>0.184310838583538</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1487994538626364</v>
+        <v>0.4980693351896269</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1781151939278609</v>
+        <v>0.2550189534699919</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1608536046518891</v>
+        <v>0.4443291831970995</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1148245463443844</v>
+        <v>0.05460827915989504</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1500178096002459</v>
+        <v>0.2055221638206967</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1477374102289877</v>
+        <v>0.02410241969682892</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="M10" s="16">
-        <v>0.09392135025615579</v>
+        <v>0.1793208037249799</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1474405319060537</v>
+        <v>0.138389977785627</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1080293781050234</v>
+        <v>0.02305130193826632</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1058011449995249</v>
+        <v>0.06675483557633163</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="D11" s="10">
-        <v>0.09610350186230514</v>
+        <v>0.02450477964460038</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="G11" s="12">
-        <v>0.06807011807375897</v>
+        <v>0.0776609178592732</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="J11" s="14">
-        <v>0.06157966512162063</v>
+        <v>0.01504190428305158</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="M11" s="16">
-        <v>0.07303039073690665</v>
+        <v>0.07143900137629855</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="P11" s="18">
-        <v>0.06955152529711095</v>
+        <v>0.06415796636452431</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="S11" s="16">
-        <v>0.09792158224420756</v>
+        <v>0.02129037815877372</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="V11" s="18">
-        <v>0.05887143874699526</v>
+        <v>0.03029184667876087</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D12" s="10">
-        <v>0.05859962967097831</v>
+        <v>0.02304509463361789</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="G12" s="12">
-        <v>0.06786983115524337</v>
+        <v>0.0679850116029919</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="J12" s="14">
-        <v>0.06036968975917228</v>
+        <v>0.01005006448682278</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="M12" s="16">
-        <v>0.0329053017664703</v>
+        <v>0.01609171070122521</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="P12" s="18">
-        <v>0.04152234863519968</v>
+        <v>0.009110187722600848</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="S12" s="16">
-        <v>0.05079305230352781</v>
+        <v>0.01493908721551784</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="V12" s="18">
-        <v>0.02667209911175297</v>
+        <v>0.01901765769520238</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D13" s="10">
-        <v>0.03302198820992513</v>
+        <v>0.01978322564285699</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="G13" s="12">
-        <v>0.04760244222874439</v>
+        <v>0.02236798538373874</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="J13" s="14">
-        <v>0.02368554552765088</v>
+        <v>0.00295872460827122</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01797265756370267</v>
+        <v>0.01452731593988784</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="P13" s="18">
-        <v>0.02899333789222501</v>
+        <v>0.007897225492648702</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="S13" s="16">
-        <v>0.0272184179438264</v>
+        <v>0.006976269367686154</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02410423164574266</v>
+        <v>0.009744226810807952</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3319,7 +3340,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3328,7 +3349,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3337,7 +3358,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3346,7 +3367,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3355,7 +3376,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3364,7 +3385,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3373,7 +3394,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3382,331 +3403,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1323563422007077</v>
+        <v>0.3391359161778072</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1436655157396998</v>
+        <v>0.1010752179660313</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1334731666180415</v>
+        <v>0.06729284954631111</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1393860611772336</v>
+        <v>0.1745397902994324</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1318407236744017</v>
+        <v>0.09077283926375551</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1474872545144458</v>
+        <v>0.2618314933809207</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="V16" s="18">
-        <v>0.3497638155559321</v>
+        <v>0.1516812750401614</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1283899515921367</v>
+        <v>0.1936046553159573</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="G17" s="12">
-        <v>0.0907406499563426</v>
+        <v>0.06921135266204244</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1318105649997194</v>
+        <v>0.02866780169439509</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1318513783000754</v>
+        <v>0.1589595455804797</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1088813990135114</v>
+        <v>0.05262098216412218</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="S17" s="16">
-        <v>0.08971247723074946</v>
+        <v>0.1430958669868743</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="V17" s="18">
-        <v>0.07203793151733187</v>
+        <v>0.08734511171367676</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D18" s="10">
-        <v>0.05000620990397842</v>
+        <v>0.09456940494051053</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="G18" s="12">
-        <v>0.04456310043575329</v>
+        <v>0.02374435546161703</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="J18" s="14">
-        <v>0.04203547194193182</v>
+        <v>0.01953276334381316</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="M18" s="16">
-        <v>0.07625729887979453</v>
+        <v>0.0481008666222087</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="P18" s="18">
-        <v>0.07729757693009534</v>
+        <v>0.04830933831653567</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="S18" s="16">
-        <v>0.08018091567173788</v>
+        <v>0.07505462839269963</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="V18" s="18">
-        <v>0.05377002478180558</v>
+        <v>0.08451763471402302</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="D19" s="10">
-        <v>0.04270975869554667</v>
+        <v>0.05029722045729898</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="G19" s="12">
-        <v>0.03119411953113028</v>
+        <v>0.02320649077625074</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="J19" s="14">
-        <v>0.03223009260163943</v>
+        <v>0.01890699320140317</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="M19" s="16">
-        <v>0.07603929268457019</v>
+        <v>0.0416204519693144</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="P19" s="18">
-        <v>0.04826100479601308</v>
+        <v>0.02885538732578616</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="S19" s="16">
-        <v>0.05396819716425996</v>
+        <v>0.07492355503748216</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02901019468983532</v>
+        <v>0.02604901180708566</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="D20" s="10">
-        <v>0.02372810862425155</v>
+        <v>0.03422224407957359</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="G20" s="12">
-        <v>0.0191976094050963</v>
+        <v>0.01324011227758339</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02979678171366431</v>
+        <v>0.0188464017103552</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="M20" s="16">
-        <v>0.05292616952770969</v>
+        <v>0.01704109093530637</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="P20" s="18">
-        <v>0.0218850916713608</v>
+        <v>0.01900796927645425</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01997610327811637</v>
+        <v>0.03034393086162373</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01772881056868639</v>
+        <v>0.0130137991540795</v>
       </c>
     </row>
   </sheetData>
